--- a/samples/수주취합/2026.09.29_납품예정 인천건기.xlsx
+++ b/samples/수주취합/2026.09.29_납품예정 인천건기.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="103">
   <si>
     <t>No</t>
   </si>
@@ -298,6 +298,9 @@
   </si>
   <si>
     <t>EA</t>
+  </si>
+  <si>
+    <t>KRW</t>
   </si>
   <si>
     <t>Z1</t>
@@ -1038,11 +1041,11 @@
       <c r="AA2" s="1">
         <v>46282.000601851854</v>
       </c>
-      <c r="AB2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>81</v>
+      <c r="AB2">
+        <v>12000</v>
+      </c>
+      <c r="AC2">
+        <v>60000</v>
       </c>
       <c r="AD2" t="s">
         <v>88</v>
@@ -1051,7 +1054,7 @@
         <v>81</v>
       </c>
       <c r="AF2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AG2" t="s">
         <v>81</v>
@@ -1093,7 +1096,7 @@
         <v>81</v>
       </c>
       <c r="AT2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AU2" t="s">
         <v>81</v>
@@ -1227,16 +1230,16 @@
         <v>82</v>
       </c>
       <c r="I3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J3" t="s">
         <v>84</v>
       </c>
       <c r="K3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M3">
         <v>0</v>
@@ -1283,11 +1286,11 @@
       <c r="AA3" s="1">
         <v>46282.000601851854</v>
       </c>
-      <c r="AB3" t="s">
-        <v>81</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>81</v>
+      <c r="AB3">
+        <v>9500</v>
+      </c>
+      <c r="AC3">
+        <v>38000</v>
       </c>
       <c r="AD3" t="s">
         <v>88</v>
@@ -1296,7 +1299,7 @@
         <v>81</v>
       </c>
       <c r="AF3" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AG3" t="s">
         <v>81</v>
@@ -1338,7 +1341,7 @@
         <v>81</v>
       </c>
       <c r="AT3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AU3" t="s">
         <v>81</v>
@@ -1472,16 +1475,16 @@
         <v>82</v>
       </c>
       <c r="I4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J4" t="s">
         <v>84</v>
       </c>
       <c r="K4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -1511,7 +1514,7 @@
         <v>81</v>
       </c>
       <c r="V4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="W4" t="s">
         <v>81</v>
@@ -1528,11 +1531,11 @@
       <c r="AA4" s="1">
         <v>46285.000601851854</v>
       </c>
-      <c r="AB4" t="s">
-        <v>81</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>81</v>
+      <c r="AB4">
+        <v>30000</v>
+      </c>
+      <c r="AC4">
+        <v>60000</v>
       </c>
       <c r="AD4" t="s">
         <v>88</v>
@@ -1541,7 +1544,7 @@
         <v>81</v>
       </c>
       <c r="AF4" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AG4" t="s">
         <v>81</v>
@@ -1583,7 +1586,7 @@
         <v>81</v>
       </c>
       <c r="AT4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AU4" t="s">
         <v>81</v>
@@ -1717,7 +1720,7 @@
         <v>82</v>
       </c>
       <c r="I5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J5" t="s">
         <v>84</v>
@@ -1773,11 +1776,11 @@
       <c r="AA5" s="1">
         <v>46286.000601851854</v>
       </c>
-      <c r="AB5" t="s">
-        <v>81</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>81</v>
+      <c r="AB5">
+        <v>12000</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
       </c>
       <c r="AD5" t="s">
         <v>88</v>
@@ -1786,7 +1789,7 @@
         <v>81</v>
       </c>
       <c r="AF5" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AG5" t="s">
         <v>81</v>
@@ -1828,7 +1831,7 @@
         <v>81</v>
       </c>
       <c r="AT5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AU5" t="s">
         <v>81</v>
@@ -1962,16 +1965,16 @@
         <v>82</v>
       </c>
       <c r="I6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J6" t="s">
         <v>84</v>
       </c>
       <c r="K6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -2018,11 +2021,11 @@
       <c r="AA6" s="1">
         <v>46286.000601851854</v>
       </c>
-      <c r="AB6" t="s">
-        <v>81</v>
-      </c>
-      <c r="AC6" t="s">
-        <v>81</v>
+      <c r="AB6">
+        <v>4000</v>
+      </c>
+      <c r="AC6">
+        <v>12000</v>
       </c>
       <c r="AD6" t="s">
         <v>88</v>
@@ -2031,7 +2034,7 @@
         <v>81</v>
       </c>
       <c r="AF6" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AG6" t="s">
         <v>81</v>
@@ -2073,7 +2076,7 @@
         <v>81</v>
       </c>
       <c r="AT6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AU6" t="s">
         <v>81</v>
